--- a/results/monthly_investor_report_2026-07-14.xlsx
+++ b/results/monthly_investor_report_2026-07-14.xlsx
@@ -646,7 +646,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1411907502446492</v>
+        <v>0.1411907281111466</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>14119.07502446492</v>
+        <v>14119.07281111465</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.211966460056985</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2992.770352214818</v>
+        <v>2992.769883058797</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>395.1010659785771</v>
@@ -1020,25 +1020,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1158182162300614</v>
+        <v>0.1158181990764193</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11581.82162300614</v>
+        <v>11581.81990764193</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1287.086980670147</v>
+        <v>1287.086829745878</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>327.7833281893649</v>
+        <v>327.7833292006644</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>280.1065641480559</v>
+        <v>280.1065641480558</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.201193097097575</v>
+        <v>2.201193164999927</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1061,25 +1061,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1004959051851134</v>
+        <v>0.1004959604649992</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10049.59051851134</v>
+        <v>10049.59604649992</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>287.3026828585149</v>
+        <v>287.3064164680217</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>395.4922768848758</v>
+        <v>395.492413687158</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2937843383926182</v>
+        <v>0.2937877395757468</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1102,25 +1102,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.08834742378690429</v>
+        <v>0.08834739475178791</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>8834.742378690429</v>
+        <v>8834.739475178791</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>679.1461580823228</v>
+        <v>679.1454050460652</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>375.2899646584571</v>
+        <v>375.2899437582186</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>325.9832118727351</v>
+        <v>325.983211872735</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.189777356656739</v>
+        <v>1.189776428449815</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.05414770455327169</v>
+        <v>0.05414771759564697</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5414.770455327169</v>
+        <v>5414.771759564697</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>162.4330022558412</v>
+        <v>162.4334405493678</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>44.90791701082177</v>
+        <v>44.90792022494814</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>41.39471417403306</v>
+        <v>41.39471417403307</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.5930838652632977</v>
+        <v>0.593085322729063</v>
       </c>
       <c r="K24" s="11" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1457,25 +1457,25 @@
         <v>384.5</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.0973111657552205</v>
+        <v>-0.09731125023654159</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>0.0474812210724069</v>
+        <v>0.0474812157001536</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>395.4922768848758</v>
+        <v>395.492413687158</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>402.7565295023405</v>
+        <v>402.7565274367091</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>347.0838567671177</v>
+        <v>347.0838242840497</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1571,25 +1571,25 @@
         <v>270.75</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-0.1075472304912292</v>
+        <v>-0.1075471744334234</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-0.0035847527809796</v>
+        <v>-0.0035848577601887</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.08512142993789459</v>
+        <v>0.0851215718148548</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>241.6315873444997</v>
+        <v>241.6316025221506</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>269.7794281845498</v>
+        <v>269.7793997614289</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>293.796627155685</v>
+        <v>293.796665568872</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>241.6315873444997</v>
+        <v>241.6316025221506</v>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
@@ -1631,22 +1631,22 @@
         <v>0.0081607762661732</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.1437536984966724</v>
+        <v>0.1437538499105514</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>297.4074289985211</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>327.7833281893649</v>
+        <v>327.7833292006644</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>337.4073410565183</v>
+        <v>337.4073857236127</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>280.1065641480559</v>
+        <v>280.1065641480558</v>
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
@@ -1685,22 +1685,22 @@
         <v>191.1000061035156</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>-0.0031018111585281</v>
+        <v>-0.0031017381985415</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.0259674251026877</v>
+        <v>0.025967427052516</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>0.0466708728798923</v>
+        <v>0.0466707608184535</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>190.5072499721889</v>
+        <v>190.5072639148428</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>196.0623811991318</v>
+        <v>196.0623815717441</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>200.0188101957195</v>
+        <v>200.0187887807778</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>181.5450057983398</v>
@@ -1745,7 +1745,7 @@
         <v>-0.0615866518007279</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>-0.0157859170736172</v>
+        <v>-0.0157857473464384</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>0.0100401434839101</v>
@@ -1754,7 +1754,7 @@
         <v>103.4131481077495</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>108.4603889349044</v>
+        <v>108.4604076388389</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>111.306420729529</v>
@@ -1802,7 +1802,7 @@
         <v>-0.0161982288834289</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
       <c r="G14" s="17" t="n">
         <v>0.2234482270298656</v>
@@ -1811,13 +1811,13 @@
         <v>342.854917234125</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>375.2899646584571</v>
+        <v>375.2899437582186</v>
       </c>
       <c r="J14" s="16" t="n">
         <v>426.3717071199082</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>325.9832118727351</v>
+        <v>325.983211872735</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>-0.0254998112759489</v>
+        <v>-0.0254997257062651</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.082112718269422</v>
+        <v>0.08211272221694969</v>
       </c>
       <c r="H15" s="19" t="n">
         <v>39.32532248816444</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>40.81206894464176</v>
+        <v>40.81207252830021</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>45.31888179694447</v>
+        <v>45.31888196226694</v>
       </c>
       <c r="K15" s="19" t="n">
         <v>39.32532248816444</v>
@@ -1973,7 +1973,7 @@
         <v>-0.0338140537472411</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>0.111591751941328</v>
@@ -1982,13 +1982,13 @@
         <v>42.12570578233753</v>
       </c>
       <c r="I17" s="16" t="n">
-        <v>44.90791701082177</v>
+        <v>44.90792022494814</v>
       </c>
       <c r="J17" s="16" t="n">
         <v>48.4653986884875</v>
       </c>
       <c r="K17" s="16" t="n">
-        <v>41.39471417403306</v>
+        <v>41.39471417403307</v>
       </c>
       <c r="L17" s="15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>0.0196644721393515</v>
+        <v>0.0196644721393516</v>
       </c>
       <c r="K4" s="17" t="n">
-        <v>0.0285884964496119</v>
+        <v>0.0285888522422834</v>
       </c>
     </row>
     <row r="5">
@@ -2311,7 +2311,7 @@
         <v>0.0227658524144454</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>-0.0035847527809796</v>
+        <v>-0.0035848577601887</v>
       </c>
     </row>
     <row r="7">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="J7" s="17" t="n">
-        <v>0.0252431116134646</v>
+        <v>0.0252431116134647</v>
       </c>
       <c r="K7" s="17" t="n">
-        <v>0.1111299260656438</v>
+        <v>0.1111299294937776</v>
       </c>
     </row>
     <row r="8">
@@ -2397,7 +2397,7 @@
         <v>0.0207599110986449</v>
       </c>
       <c r="K8" s="23" t="n">
-        <v>0.0259674251026877</v>
+        <v>0.025967427052516</v>
       </c>
     </row>
     <row r="9">
@@ -2440,7 +2440,7 @@
         <v>0.0216927332752226</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>-0.0157859170736172</v>
+        <v>-0.0157857473464384</v>
       </c>
     </row>
     <row r="10">
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.0323052914307962</v>
+        <v>0.0323052914307963</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>0.0768722084891164</v>
+        <v>0.07687214851712661</v>
       </c>
     </row>
     <row r="11">
@@ -2526,7 +2526,7 @@
         <v>0.0268438090323615</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>-0.0254998112759489</v>
+        <v>-0.0254997257062651</v>
       </c>
     </row>
     <row r="12">
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.0252899584548952</v>
+        <v>0.0252899584548951</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>0.029998132625555</v>
+        <v>0.0299982063440521</v>
       </c>
     </row>
     <row r="14">
@@ -2698,7 +2698,7 @@
         <v>0.0238212180877457</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0.0044790800861671</v>
+        <v>0.0044791569432763</v>
       </c>
     </row>
     <row r="16">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0294479348541073</v>
+        <v>0.0294479348541072</v>
       </c>
       <c r="K16" s="28" t="n">
-        <v>0.0024287491670588</v>
+        <v>0.0024286871265271</v>
       </c>
     </row>
     <row r="17">
@@ -2784,7 +2784,7 @@
         <v>0.0226186848606233</v>
       </c>
       <c r="K17" s="28" t="n">
-        <v>0.0283622708857007</v>
+        <v>0.0283623502202803</v>
       </c>
     </row>
     <row r="18">
@@ -2827,7 +2827,7 @@
         <v>0.0165054412771882</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>0.0423503831348128</v>
+        <v>0.0423504428390855</v>
       </c>
     </row>
     <row r="19">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="J19" s="28" t="n">
-        <v>0.0294480866932792</v>
+        <v>0.0294480866932793</v>
       </c>
       <c r="K19" s="28" t="n">
         <v>0.06673212298112791</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="J20" s="28" t="n">
-        <v>0.0200612149228342</v>
+        <v>0.0200612149228341</v>
       </c>
       <c r="K20" s="28" t="inlineStr"/>
     </row>
@@ -2944,7 +2944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3063,7 +3063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3314,7 +3314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14080</v>
+        <v>14251.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12745.84003417969</v>
+        <v>12760.26203125</v>
       </c>
     </row>
     <row r="6">
@@ -3439,7 +3439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-07-16 04:47</t>
+          <t>Son Güncelleme: 2026-07-17 04:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
